--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487002_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487002_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.091200000000001</v>
+        <v>7.9553</v>
       </c>
       <c r="E2" t="n">
-        <v>3.1475</v>
+        <v>3.5156</v>
       </c>
       <c r="F2" t="n">
-        <v>4.9437</v>
+        <v>4.4398</v>
       </c>
       <c r="G2" t="n">
         <v>0.4313</v>
@@ -610,13 +610,13 @@
         <v>3.2855</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0375</v>
+        <v>-0.1733</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.2129</v>
+        <v>-0.8448</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1754</v>
+        <v>0.6715</v>
       </c>
       <c r="V2" t="n">
         <v>5.6439</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.2225</v>
+        <v>4.8302</v>
       </c>
       <c r="E3" t="n">
-        <v>2.347</v>
+        <v>2.6879</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8755</v>
+        <v>2.1423</v>
       </c>
       <c r="G3" t="n">
         <v>-0.6907</v>
@@ -688,13 +688,13 @@
         <v>2.2588</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.0387</v>
+        <v>-0.431</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.1198</v>
+        <v>-0.7789</v>
       </c>
       <c r="U3" t="n">
-        <v>0.08110000000000001</v>
+        <v>0.3479</v>
       </c>
       <c r="V3" t="n">
         <v>3.8985</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. KANE</t>
+          <t>B. ALVAREZ TORRES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5709</v>
+        <v>1.2372</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1587</v>
+        <v>1.5552</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7296</v>
+        <v>-0.3181</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4864</v>
+        <v>0.7343</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.07140000000000001</v>
+        <v>0.9344</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5579</v>
+        <v>-0.2</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0389</v>
+        <v>1.9544</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0389</v>
+        <v>0.9023</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.0522</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4475</v>
+        <v>-1.2201</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1104</v>
+        <v>0.0321</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5579</v>
+        <v>-1.2522</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2053</v>
+        <v>2.0534</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2053</v>
+        <v>2.0534</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1208</v>
+        <v>-0.372</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1976</v>
+        <v>-0.3992</v>
       </c>
       <c r="U4" t="n">
-        <v>0.07679999999999999</v>
+        <v>0.0272</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B. ALVAREZ TORRES</t>
+          <t>S. KANE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3453</v>
+        <v>0.6162</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9005</v>
+        <v>-0.0541</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5552</v>
+        <v>0.6703</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7343</v>
+        <v>0.4864</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9344</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2</v>
+        <v>0.5579</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9544</v>
+        <v>0.0389</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9023</v>
+        <v>0.0389</v>
       </c>
       <c r="L5" t="n">
-        <v>1.0522</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.2201</v>
+        <v>0.4475</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0321</v>
+        <v>-0.1104</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.2522</v>
+        <v>0.5579</v>
       </c>
       <c r="P5" t="n">
-        <v>2.0534</v>
+        <v>0.2053</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0534</v>
+        <v>0.2053</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.2638</v>
+        <v>-0.0755</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.054</v>
+        <v>-0.093</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2099</v>
+        <v>0.0175</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3749</v>
+        <v>-0.3453</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3749</v>
+        <v>-0.3453</v>
       </c>
       <c r="G8" t="n">
         <v>-0.3947</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0198</v>
+        <v>0.0494</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0198</v>
+        <v>0.0494</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C. LAROUSSE</t>
+          <t>X. TORRENT BAYÉ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2159</v>
+        <v>-0.3456</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.403</v>
+        <v>-1.0709</v>
       </c>
       <c r="F9" t="n">
-        <v>0.187</v>
+        <v>0.7254</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0469</v>
+        <v>-2.1124</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7335</v>
+        <v>0.5187</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6866</v>
+        <v>-2.6312</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8094</v>
+        <v>-0.382</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7305</v>
+        <v>0.4866</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0789</v>
+        <v>-0.8686</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7625999999999999</v>
+        <v>-1.7305</v>
       </c>
       <c r="N9" t="n">
-        <v>0.003</v>
+        <v>0.0321</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.7655999999999999</v>
+        <v>-1.7626</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2053</v>
+        <v>1.2321</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.0534</v>
+        <v>-1.2321</v>
       </c>
       <c r="R9" t="n">
-        <v>2.2588</v>
+        <v>2.4641</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0493</v>
+        <v>-0.526</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.159</v>
+        <v>-0.6355</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1097</v>
+        <v>0.1096</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.4189</v>
+        <v>1.0608</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.4189</v>
+        <v>-0.1179</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X. TORRENT BAYÉ</t>
+          <t>C. LAROUSSE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.3404</v>
+        <v>-1.2045</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6211</v>
+        <v>-1.4805</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2807</v>
+        <v>0.276</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.1124</v>
+        <v>0.0469</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5187</v>
+        <v>0.7335</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.6312</v>
+        <v>-0.6866</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.382</v>
+        <v>0.8094</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4866</v>
+        <v>0.7305</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.8686</v>
+        <v>0.0789</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.7305</v>
+        <v>-0.7625999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0321</v>
+        <v>0.003</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.7626</v>
+        <v>-0.7655999999999999</v>
       </c>
       <c r="P10" t="n">
-        <v>1.2321</v>
+        <v>0.2053</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.2321</v>
+        <v>-2.0534</v>
       </c>
       <c r="R10" t="n">
-        <v>2.4641</v>
+        <v>2.2588</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.5208</v>
+        <v>-0.0378</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1857</v>
+        <v>-0.2364</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3351</v>
+        <v>0.1986</v>
       </c>
       <c r="V10" t="n">
-        <v>1.0608</v>
+        <v>-1.4189</v>
       </c>
       <c r="W10" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1179</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. MIKHAILOV PALTARAK</t>
+          <t>I. VALERA COROMINAS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.5118</v>
+        <v>-2.2661</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.3057</v>
+        <v>-3.2235</v>
       </c>
       <c r="F11" t="n">
-        <v>2.7939</v>
+        <v>0.9574</v>
       </c>
       <c r="G11" t="n">
-        <v>0.08400000000000001</v>
+        <v>-1.8972</v>
       </c>
       <c r="H11" t="n">
-        <v>1.8202</v>
+        <v>-0.4056</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.7361</v>
+        <v>-1.4917</v>
       </c>
       <c r="J11" t="n">
-        <v>2.0981</v>
+        <v>-1.235</v>
       </c>
       <c r="K11" t="n">
-        <v>1.9797</v>
+        <v>-0.5770999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1184</v>
+        <v>-0.6579</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.0141</v>
+        <v>-0.6622</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1596</v>
+        <v>0.1716</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.8545</v>
+        <v>-0.8338</v>
       </c>
       <c r="P11" t="n">
-        <v>-4.3122</v>
+        <v>0.4107</v>
       </c>
       <c r="Q11" t="n">
-        <v>-8.419</v>
+        <v>-1.0267</v>
       </c>
       <c r="R11" t="n">
-        <v>4.1068</v>
+        <v>1.4374</v>
       </c>
       <c r="S11" t="n">
-        <v>1.5242</v>
+        <v>0.1589</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1159</v>
+        <v>-0.2636</v>
       </c>
       <c r="U11" t="n">
-        <v>1.4083</v>
+        <v>0.4225</v>
       </c>
       <c r="V11" t="n">
-        <v>1.1922</v>
+        <v>-0.9384</v>
       </c>
       <c r="W11" t="n">
-        <v>1.8993</v>
+        <v>-0.6982</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.7072000000000001</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>I. VALERA COROMINAS</t>
+          <t>M. MIKHAILOV PALTARAK</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.2273</v>
+        <v>-2.6641</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.1848</v>
+        <v>-4.9836</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9574</v>
+        <v>2.3196</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.8972</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4056</v>
+        <v>1.8202</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.4917</v>
+        <v>-1.7361</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.235</v>
+        <v>2.0981</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.5770999999999999</v>
+        <v>1.9797</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6579</v>
+        <v>0.1184</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.6622</v>
+        <v>-2.0141</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1716</v>
+        <v>-0.1596</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.8338</v>
+        <v>-1.8545</v>
       </c>
       <c r="P12" t="n">
-        <v>0.4107</v>
+        <v>-4.3122</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.0267</v>
+        <v>-8.419</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4374</v>
+        <v>4.1068</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1976</v>
+        <v>0.372</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2249</v>
+        <v>-0.5620000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4225</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.9384</v>
+        <v>1.1922</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.6982</v>
+        <v>1.8993</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.2402</v>
+        <v>-0.7072000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.8195</v>
+        <v>-3.7562</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.1782</v>
+        <v>-3.0852</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.6413</v>
+        <v>-0.6709000000000001</v>
       </c>
       <c r="G13" t="n">
         <v>-3.0987</v>
@@ -1468,13 +1468,13 @@
         <v>3.0801</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.291</v>
+        <v>-0.2276</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8177</v>
+        <v>-0.7247</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5266999999999999</v>
+        <v>0.4971</v>
       </c>
       <c r="V13" t="n">
         <v>-3.3047</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.429700000000002</v>
+        <v>3.7467</v>
       </c>
       <c r="E14" t="n">
-        <v>-7.588200000000001</v>
+        <v>-6.270799999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>10.0177</v>
+        <v>10.0178</v>
       </c>
       <c r="G14" t="n">
         <v>-7.0002</v>
       </c>
       <c r="H14" t="n">
-        <v>4.0237</v>
+        <v>4.023700000000001</v>
       </c>
       <c r="I14" t="n">
         <v>-11.0237</v>
@@ -1537,7 +1537,7 @@
         <v>-6.4835</v>
       </c>
       <c r="P14" t="n">
-        <v>7.1869</v>
+        <v>7.186899999999998</v>
       </c>
       <c r="Q14" t="n">
         <v>-14.3739</v>
@@ -1546,10 +1546,10 @@
         <v>21.5609</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.711999999999999</v>
+        <v>-1.3946</v>
       </c>
       <c r="T14" t="n">
-        <v>-5.9874</v>
+        <v>-4.6698</v>
       </c>
       <c r="U14" t="n">
         <v>3.2753</v>
@@ -1561,7 +1561,7 @@
         <v>11.9402</v>
       </c>
       <c r="X14" t="n">
-        <v>-6.985600000000001</v>
+        <v>-6.9856</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.7446</v>
+        <v>7.3374</v>
       </c>
       <c r="E15" t="n">
         <v>4.2962</v>
       </c>
       <c r="F15" t="n">
-        <v>2.4484</v>
+        <v>3.0413</v>
       </c>
       <c r="G15" t="n">
         <v>5.5312</v>
@@ -1624,13 +1624,13 @@
         <v>2.0534</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5115</v>
+        <v>0.0813</v>
       </c>
       <c r="T15" t="n">
         <v>-0.6860000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1744</v>
+        <v>0.7673</v>
       </c>
       <c r="V15" t="n">
         <v>0.6982</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.8691</v>
+        <v>2.36</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3175</v>
+        <v>0.6898</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5516</v>
+        <v>1.6702</v>
       </c>
       <c r="G16" t="n">
         <v>2.267</v>
@@ -1702,13 +1702,13 @@
         <v>1.4374</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6369</v>
+        <v>0.1279</v>
       </c>
       <c r="T16" t="n">
-        <v>0.736</v>
+        <v>0.1084</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.09909999999999999</v>
+        <v>0.0195</v>
       </c>
       <c r="V16" t="n">
         <v>-0.2402</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B. TRAORE</t>
+          <t>D. CUELLAR GARCIA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.7991</v>
+        <v>2.0993</v>
       </c>
       <c r="E17" t="n">
-        <v>1.1228</v>
+        <v>0.9854000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>1.6763</v>
+        <v>1.1139</v>
       </c>
       <c r="G17" t="n">
-        <v>1.2978</v>
+        <v>4.7762</v>
       </c>
       <c r="H17" t="n">
-        <v>1.2005</v>
+        <v>0.7848000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0973</v>
+        <v>3.9914</v>
       </c>
       <c r="J17" t="n">
-        <v>1.2466</v>
+        <v>3.4652</v>
       </c>
       <c r="K17" t="n">
-        <v>1.9179</v>
+        <v>0.3343</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6713</v>
+        <v>3.1308</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0512</v>
+        <v>1.3111</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7174</v>
+        <v>0.4505</v>
       </c>
       <c r="O17" t="n">
-        <v>0.7685999999999999</v>
+        <v>0.8606</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.2321</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.0801</v>
+        <v>-2.0534</v>
       </c>
       <c r="R17" t="n">
         <v>1.8481</v>
       </c>
       <c r="S17" t="n">
-        <v>3.7807</v>
+        <v>0.3662</v>
       </c>
       <c r="T17" t="n">
-        <v>1.4061</v>
+        <v>-0.4263</v>
       </c>
       <c r="U17" t="n">
-        <v>2.3746</v>
+        <v>0.7925</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.0472</v>
+        <v>-2.8377</v>
       </c>
       <c r="W17" t="n">
-        <v>1.5503</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.5975</v>
+        <v>-2.8377</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. CUELLAR GARCIA</t>
+          <t>J. SÁNCHEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.531</v>
+        <v>1.8351</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3578</v>
+        <v>3.1452</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1732</v>
+        <v>-1.3101</v>
       </c>
       <c r="G18" t="n">
-        <v>4.7762</v>
+        <v>0.2439</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7848000000000001</v>
+        <v>-1.2003</v>
       </c>
       <c r="I18" t="n">
-        <v>3.9914</v>
+        <v>1.4442</v>
       </c>
       <c r="J18" t="n">
-        <v>3.4652</v>
+        <v>-0.038</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3343</v>
+        <v>-1.0638</v>
       </c>
       <c r="L18" t="n">
-        <v>3.1308</v>
+        <v>1.0257</v>
       </c>
       <c r="M18" t="n">
-        <v>1.3111</v>
+        <v>0.2819</v>
       </c>
       <c r="N18" t="n">
-        <v>0.4505</v>
+        <v>-0.1365</v>
       </c>
       <c r="O18" t="n">
-        <v>0.8606</v>
+        <v>0.4184</v>
       </c>
       <c r="P18" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="Q18" t="n">
         <v>-0.2053</v>
       </c>
-      <c r="Q18" t="n">
-        <v>-2.0534</v>
-      </c>
       <c r="R18" t="n">
-        <v>1.8481</v>
+        <v>0.8214</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2022</v>
+        <v>-0.2034</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.054</v>
+        <v>-0.1473</v>
       </c>
       <c r="U18" t="n">
-        <v>0.8518</v>
+        <v>-0.0561</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.8377</v>
+        <v>1.1786</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>3.5359</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.8377</v>
+        <v>-2.3573</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. SÁNCHEZ</t>
+          <t>B. TRAORE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.3435</v>
+        <v>0.7872</v>
       </c>
       <c r="E19" t="n">
-        <v>2.8314</v>
+        <v>-0.237</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.4879</v>
+        <v>1.0242</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2439</v>
+        <v>1.2978</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.2003</v>
+        <v>1.2005</v>
       </c>
       <c r="I19" t="n">
-        <v>1.4442</v>
+        <v>0.0973</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.038</v>
+        <v>1.2466</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.0638</v>
+        <v>1.9179</v>
       </c>
       <c r="L19" t="n">
-        <v>1.0257</v>
+        <v>-0.6713</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2819</v>
+        <v>0.0512</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1365</v>
+        <v>-0.7174</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4184</v>
+        <v>0.7685999999999999</v>
       </c>
       <c r="P19" t="n">
-        <v>0.616</v>
+        <v>-1.2321</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.2053</v>
+        <v>-3.0801</v>
       </c>
       <c r="R19" t="n">
-        <v>0.8214</v>
+        <v>1.8481</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6951000000000001</v>
+        <v>1.7687</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4611</v>
+        <v>0.0463</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.234</v>
+        <v>1.7224</v>
       </c>
       <c r="V19" t="n">
-        <v>1.1786</v>
+        <v>-1.0472</v>
       </c>
       <c r="W19" t="n">
-        <v>3.5359</v>
+        <v>1.5503</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.3573</v>
+        <v>-2.5975</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.1595</v>
+        <v>0.7288</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5151</v>
+        <v>-0.6197</v>
       </c>
       <c r="F20" t="n">
-        <v>1.6746</v>
+        <v>1.3485</v>
       </c>
       <c r="G20" t="n">
         <v>1.8184</v>
@@ -2014,13 +2014,13 @@
         <v>0.8214</v>
       </c>
       <c r="S20" t="n">
-        <v>0.7784</v>
+        <v>0.3478</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2362</v>
+        <v>0.1316</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5422</v>
+        <v>0.2161</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5864</v>
+        <v>-0.3475</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.2525</v>
+        <v>-1.0433</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6661</v>
+        <v>0.6957</v>
       </c>
       <c r="G21" t="n">
         <v>-0.672</v>
@@ -2092,13 +2092,13 @@
         <v>1.0267</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7357</v>
+        <v>-0.4969</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5928</v>
+        <v>-0.3836</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1429</v>
+        <v>-0.1132</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.8005</v>
+        <v>-3.7535</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.2577</v>
+        <v>-2.9439</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5427999999999999</v>
+        <v>-0.8096</v>
       </c>
       <c r="G22" t="n">
         <v>-1.8397</v>
@@ -2170,13 +2170,13 @@
         <v>0.8214</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2097</v>
+        <v>0.2567</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9222</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>1.1319</v>
+        <v>0.8651</v>
       </c>
       <c r="V22" t="n">
         <v>-0.9384</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.3763</v>
+        <v>-5.5865</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.2957</v>
+        <v>-4.7727</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.0806</v>
+        <v>-0.8138</v>
       </c>
       <c r="G23" t="n">
         <v>-1.7056</v>
@@ -2248,13 +2248,13 @@
         <v>1.6427</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6358</v>
+        <v>0.154</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.2516</v>
+        <v>-0.7286</v>
       </c>
       <c r="U23" t="n">
-        <v>0.6158</v>
+        <v>0.8826000000000001</v>
       </c>
       <c r="V23" t="n">
         <v>-2.5975</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-8.113099999999999</v>
+        <v>-7.89</v>
       </c>
       <c r="E24" t="n">
-        <v>-9.6225</v>
+        <v>-9.517899999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>1.5094</v>
+        <v>1.6279</v>
       </c>
       <c r="G24" t="n">
         <v>-4.7173</v>
@@ -2326,13 +2326,13 @@
         <v>2.0534</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0868</v>
+        <v>0.3099</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6860000000000001</v>
+        <v>-0.5814</v>
       </c>
       <c r="U24" t="n">
-        <v>0.7727000000000001</v>
+        <v>0.8913</v>
       </c>
       <c r="V24" t="n">
         <v>0.8295</v>
@@ -2359,19 +2359,19 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.4295</v>
+        <v>-2.429699999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>-10.0178</v>
+        <v>-10.0179</v>
       </c>
       <c r="F25" t="n">
-        <v>7.588300000000001</v>
+        <v>7.588200000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>6.999899999999998</v>
+        <v>6.9999</v>
       </c>
       <c r="H25" t="n">
-        <v>-4.023700000000001</v>
+        <v>-4.0237</v>
       </c>
       <c r="I25" t="n">
         <v>11.0236</v>
@@ -2380,13 +2380,13 @@
         <v>7.833000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>1.349699999999999</v>
+        <v>1.3497</v>
       </c>
       <c r="L25" t="n">
         <v>6.483199999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.8329000000000001</v>
+        <v>-0.8328999999999999</v>
       </c>
       <c r="N25" t="n">
         <v>-5.373200000000001</v>
@@ -2407,10 +2407,10 @@
         <v>2.7122</v>
       </c>
       <c r="T25" t="n">
-        <v>-3.2754</v>
+        <v>-3.2753</v>
       </c>
       <c r="U25" t="n">
-        <v>5.9874</v>
+        <v>5.9875</v>
       </c>
       <c r="V25" t="n">
         <v>-4.9547</v>
